--- a/docs/plan/TEA-PLAN-001_development-plan.xlsx
+++ b/docs/plan/TEA-PLAN-001_development-plan.xlsx
@@ -1,37 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contents" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Objectives" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scope" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Principles" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Components" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence_Model" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Query_Handling" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Policy" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Scope" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_App" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delivery_Steps" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommendations" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Items" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Version_Control" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Contents" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Objectives" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Scope" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Principles" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Components" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Confidence_Model" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Query_Handling" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="LLM_Policy" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Data_Model" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Review_Scope" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Architecture" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Web_App" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Delivery_Steps" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Requirements" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Risks" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Metrics" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Recommendations" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Decisions" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Open_Items" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Validation" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Version_Control" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Assumptions" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Glossary" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="References" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Objectives'!$A$3:$G$12</definedName>
@@ -704,7 +704,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>1.5.0</t>
+          <t>1.6.0</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>v1.4.0, issued 2026-08-22</t>
+          <t>v1.5.0, issued 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>TEA-SPEC-001 v2.0.0 — APPROVED 2026-08-21, rule pack frozen</t>
+          <t>TEA-SPEC-001 v2.6.0 — APPROVED, rule pack frozen at 2.0.0</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7455,12 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Supplementary query-history input. Specified on the SDTM_Requirements sheet as the QUERY* row, marked required.</t>
+          <t>DRAFTED 2026-09-12 as TEA-CTR-004, on the specification's Query_History sheet, from a real Veeva Query Detail export. Three confirmations remain: (a) a second export containing manual, site-answered queries, because this one has none and the LLM answer-assessment path is therefore unexercised; (b) that Item Group Sequence Number identifies the lesion row on a repeating tumour form, which this export could not show; (c) the full Query Status vocabulary, since only Open and Closed appear.</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>5 rules and the entire query reconciliation model depend on it. Without it the agent re-raises every finding at every data cut, which is the behaviour OBJ-04 was written to prevent. It is the largest single gap in an SDTM-only delivery.</t>
+          <t>Six TE-QM rules and the whole query reconciliation model depend on it. The export resolved more than expected — the correction fact turns out to be carried deterministically — but it also showed that lesion-level matching rests on a single sequence number that must survive the SDTM conversion.</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>Confirm it can be extracted from Veeva</t>
+          <t>Second export before Step 3</t>
         </is>
       </c>
     </row>
@@ -10067,8 +10067,8 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B12:D12"/>

--- a/docs/plan/TEA-PLAN-001_development-plan.xlsx
+++ b/docs/plan/TEA-PLAN-001_development-plan.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>1.6.0</t>
+          <t>1.7.0</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>v1.5.0, issued 2026-08-22</t>
+          <t>v1.6.0, issued 2026-09-12</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>TEA-SPEC-001 v2.6.0 — APPROVED, rule pack frozen at 2.0.0</t>
+          <t>TEA-SPEC-001 v2.7.0 — APPROVED, rule pack frozen at 2.0.0</t>
         </is>
       </c>
     </row>
@@ -7180,7 +7180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7471,6 +7471,33 @@
       <c r="E12" s="21" t="inlineStr">
         <is>
           <t>Second export before Step 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>OI-10</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Imaging charter access and extract. TEA-CTR-005 defines what the agent needs from the charter; the extract itself is APPLY slot A-08 and cannot be produced outside the company. Eight of the 34 parameters are routinely stated in the protocol too, and ten more sometimes are, so up to half can disagree.</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Until a real charter is read, the conflict-resolution path (AC-11 leaving a parameter unresolved and asking the study team) is specified but unexercised. It is also the path that most affects configuration correctness.</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>CDM + Medical Monitor</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Before Step 3 output is reviewed</t>
         </is>
       </c>
     </row>
